--- a/templates/000_pm_suite/02_프로젝트 개발/03_분석/04_요구사항검토/프로젝트명_품질체크리스트_V1.0_20230530.xlsx
+++ b/templates/000_pm_suite/02_프로젝트 개발/03_분석/04_요구사항검토/프로젝트명_품질체크리스트_V1.0_20230530.xlsx
@@ -518,7 +518,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-34] SyncGuard AI 요구사항 분석 단계 산출물 품질 검토 체크리스트 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-34] SyncFlow AI 요구사항 분석 단계 산출물 품질 검토 체크리스트 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>HB-SSO, ProductLab(02:00 일배치), MarketingHub(Webhook) 연계 전문 규격 및 장애 대책이 합의되었는가?</t>
+          <t>HB-SSO, PLM-Nexus(02:00 일배치), SRM-Portal(Webhook) 연계 전문 규격 및 장애 대책이 합의되었는가?</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>100대 규제 룰셋 및 골든셋(500건)의 현업 규제심의팀 감수 절차가 정의되었는가?</t>
+          <t>100대 규제 룰셋 및 골든셋(500건)의 현업 규제검증팀 감수 절차가 정의되었는가?</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>규제심의팀 윤서연 팀장 감수 및 버전 관리 절차 확정</t>
+          <t>규제검증팀 윤서연 팀장 감수 및 버전 관리 절차 확정</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
